--- a/data/output/sim_gridrnd/REL1/group_480_20/results/REL1_G1_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_480_20/results/REL1_G1_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>479</v>
       </c>
       <c r="C2" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D2" t="n">
         <v>22</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E2" t="n">
         <v>479</v>
@@ -852,1212 +907,1377 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>478.8219401540162</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14.39358340699369</v>
-      </c>
-      <c r="K2" t="n">
-        <v>480.9377029698776</v>
-      </c>
-      <c r="L2" t="n">
-        <v>18.21903216948061</v>
-      </c>
-      <c r="M2" t="n">
-        <v>479.4197599335436</v>
-      </c>
-      <c r="N2" t="n">
-        <v>21.96005381553079</v>
-      </c>
-      <c r="O2" t="n">
-        <v>478.5636455307291</v>
-      </c>
-      <c r="P2" t="n">
-        <v>24.77662822370057</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>479.3555054793794</v>
-      </c>
       <c r="R2" t="n">
-        <v>25.56649485586474</v>
+        <v>478.82</v>
       </c>
       <c r="S2" t="n">
-        <v>482.0928566879388</v>
+        <v>14.39</v>
       </c>
       <c r="T2" t="n">
-        <v>26.2728168206648</v>
+        <v>480.94</v>
       </c>
       <c r="U2" t="n">
-        <v>480.2648279073637</v>
+        <v>18.22</v>
       </c>
       <c r="V2" t="n">
-        <v>25.0891366209012</v>
+        <v>479.42</v>
       </c>
       <c r="W2" t="n">
-        <v>477.8265140799369</v>
+        <v>21.96</v>
       </c>
       <c r="X2" t="n">
-        <v>26.88006822279444</v>
+        <v>478.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>477.7959871724061</v>
+        <v>24.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.85799960502565</v>
+        <v>479.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>25.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>482.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>26.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>480.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>25.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>477.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>26.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>477.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>25.86</v>
       </c>
       <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>503.675</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>503</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>502.975</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>502.43</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>501.4333333333333</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>501.3928571428572</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>501.325</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>501.5333333333334</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>500.95</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>51.69980053153009</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>45.59056920021947</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>42.88180703981585</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>42.14125176119001</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>42.81661152195748</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>41.00203765469143</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>39.12329069748607</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>38.57912504047867</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>39.19499330271661</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>380</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>380</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>380</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>380</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>380</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>380</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>380</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>380</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>380</v>
       </c>
-      <c r="BK2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>669</v>
-      </c>
       <c r="BT2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CD2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="CE2" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.88</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.8275862068965517</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.8717948717948718</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.9743589743589743</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>25.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G1_478_18_REL1</t>
+          <t>S02_G1_481_20_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D3" t="n">
-        <v>26.68643439584878</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>486.8806542340598</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20.5382054013764</v>
-      </c>
-      <c r="K3" t="n">
-        <v>477.044122882953</v>
-      </c>
-      <c r="L3" t="n">
-        <v>26.14956841765691</v>
-      </c>
-      <c r="M3" t="n">
-        <v>477.5688223341439</v>
-      </c>
-      <c r="N3" t="n">
-        <v>25.50254758584148</v>
-      </c>
-      <c r="O3" t="n">
-        <v>479.2280742871174</v>
-      </c>
-      <c r="P3" t="n">
-        <v>25.52383326521343</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>476.258363670722</v>
-      </c>
       <c r="R3" t="n">
-        <v>26.29620255439587</v>
+        <v>477.5</v>
       </c>
       <c r="S3" t="n">
-        <v>476.8200372242777</v>
+        <v>22.03</v>
       </c>
       <c r="T3" t="n">
-        <v>25.90417815387672</v>
+        <v>479.17</v>
       </c>
       <c r="U3" t="n">
-        <v>478.9802655841302</v>
+        <v>25.35</v>
       </c>
       <c r="V3" t="n">
-        <v>24.32253685345409</v>
+        <v>477.35</v>
       </c>
       <c r="W3" t="n">
-        <v>480.3725710801103</v>
+        <v>22.74</v>
       </c>
       <c r="X3" t="n">
-        <v>22.5419780933512</v>
+        <v>479.81</v>
       </c>
       <c r="Y3" t="n">
-        <v>480.2745715846892</v>
+        <v>27.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.18195794096333</v>
+        <v>480.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>24.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>475.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>24.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>476.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>23.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>475.86</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>477.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>22.82</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500.625</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>499.95</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>501.3875</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>499.66</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>500.2416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>501.1214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>504.475</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>502.6333333333333</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>501.8625</v>
+      </c>
+      <c r="AV3" t="n">
         <v>500.65</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>499.9944444444445</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>499.635</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>54.39792620128087</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>54.90671634690969</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>53.32412534444423</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>51.32040919556273</v>
-      </c>
       <c r="AW3" t="n">
-        <v>52.23616177728052</v>
+        <v>501.05</v>
       </c>
       <c r="AX3" t="n">
-        <v>49.3234901813879</v>
+        <v>500.2357142857143</v>
       </c>
       <c r="AY3" t="n">
-        <v>48.01903268496774</v>
+        <v>500.66875</v>
       </c>
       <c r="AZ3" t="n">
-        <v>46.53057504029202</v>
+        <v>500.7722222222222</v>
       </c>
       <c r="BA3" t="n">
-        <v>44.36250415610012</v>
+        <v>500.765</v>
       </c>
       <c r="BB3" t="n">
-        <v>361</v>
+        <v>56.19296552950378</v>
       </c>
       <c r="BC3" t="n">
-        <v>361</v>
+        <v>50.59149028135946</v>
       </c>
       <c r="BD3" t="n">
-        <v>361</v>
+        <v>46.84275390868901</v>
       </c>
       <c r="BE3" t="n">
-        <v>361</v>
+        <v>46.9734765585857</v>
       </c>
       <c r="BF3" t="n">
-        <v>361</v>
+        <v>44.19197702449318</v>
       </c>
       <c r="BG3" t="n">
-        <v>361</v>
+        <v>42.95240068366139</v>
       </c>
       <c r="BH3" t="n">
-        <v>361</v>
+        <v>42.50834063378033</v>
       </c>
       <c r="BI3" t="n">
-        <v>361</v>
+        <v>41.7650612295274</v>
       </c>
       <c r="BJ3" t="n">
-        <v>361</v>
+        <v>41.12152447320016</v>
       </c>
       <c r="BK3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BL3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BM3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BN3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BO3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BP3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BQ3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BR3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BS3" t="n">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="BT3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="CF3" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU3" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.9545454545454546</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0.8666666666666667</v>
+      <c r="CG3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>477.15</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>22.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S02_G1_481_20_REL1</t>
+          <t>S03_G1_478_18_REL1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D4" t="n">
-        <v>29.65159377316531</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>477.4983158979752</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22.03111442212306</v>
-      </c>
-      <c r="K4" t="n">
-        <v>479.1713113612087</v>
-      </c>
-      <c r="L4" t="n">
-        <v>25.34890202141326</v>
-      </c>
-      <c r="M4" t="n">
-        <v>477.3543184945672</v>
-      </c>
-      <c r="N4" t="n">
-        <v>22.74062434704296</v>
-      </c>
-      <c r="O4" t="n">
-        <v>479.8057701296118</v>
-      </c>
-      <c r="P4" t="n">
-        <v>27.0852598990371</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>480.1986564107988</v>
-      </c>
       <c r="R4" t="n">
-        <v>24.36519178823171</v>
+        <v>486.88</v>
       </c>
       <c r="S4" t="n">
-        <v>475.2534653940785</v>
+        <v>20.54</v>
       </c>
       <c r="T4" t="n">
-        <v>24.77970012068528</v>
+        <v>477.04</v>
       </c>
       <c r="U4" t="n">
-        <v>476.3124826130412</v>
+        <v>26.15</v>
       </c>
       <c r="V4" t="n">
-        <v>23.41770910588357</v>
+        <v>477.57</v>
       </c>
       <c r="W4" t="n">
-        <v>475.8595424862218</v>
+        <v>25.5</v>
       </c>
       <c r="X4" t="n">
-        <v>24.09529886699581</v>
+        <v>479.23</v>
       </c>
       <c r="Y4" t="n">
-        <v>477.1461623570622</v>
+        <v>25.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.82449747267391</v>
+        <v>476.26</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>476.82</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>478.98</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>24.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>480.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>22.54</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>480.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>23.18</v>
       </c>
       <c r="AJ4" t="n">
-        <v>504.475</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>502.6333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>501.8625</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>500.625</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>499.95</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>501.3875</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>499.66</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>500.2416666666667</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>501.1214285714286</v>
+      </c>
+      <c r="AY4" t="n">
         <v>500.65</v>
       </c>
-      <c r="AN4" t="n">
-        <v>501.05</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>500.2357142857143</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>500.66875</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>500.7722222222222</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>500.765</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>56.19296552950378</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>50.59149028135946</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>46.84275390868901</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>46.9734765585857</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>44.19197702449318</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>42.95240068366139</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>42.50834063378033</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>41.7650612295274</v>
+        <v>499.9944444444445</v>
       </c>
       <c r="BA4" t="n">
-        <v>41.12152447320016</v>
+        <v>499.635</v>
       </c>
       <c r="BB4" t="n">
-        <v>382</v>
+        <v>54.39792620128087</v>
       </c>
       <c r="BC4" t="n">
-        <v>382</v>
+        <v>54.90671634690969</v>
       </c>
       <c r="BD4" t="n">
-        <v>382</v>
+        <v>53.32412534444423</v>
       </c>
       <c r="BE4" t="n">
-        <v>382</v>
+        <v>51.32040919556273</v>
       </c>
       <c r="BF4" t="n">
-        <v>382</v>
+        <v>52.23616177728052</v>
       </c>
       <c r="BG4" t="n">
-        <v>382</v>
+        <v>49.3234901813879</v>
       </c>
       <c r="BH4" t="n">
-        <v>382</v>
+        <v>48.01903268496774</v>
       </c>
       <c r="BI4" t="n">
-        <v>382</v>
+        <v>46.53057504029202</v>
       </c>
       <c r="BJ4" t="n">
-        <v>382</v>
+        <v>44.36250415610012</v>
       </c>
       <c r="BK4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BL4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BM4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BN4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BO4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BP4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BQ4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BR4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BS4" t="n">
-        <v>669</v>
+        <v>361</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK4" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BV4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.8787878787878788</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0.9444444444444444</v>
+      <c r="CL4" t="n">
+        <v>480.27</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>23.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G1_481_21_REL1</t>
+          <t>S04_G1_478_22_REL1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D5" t="n">
-        <v>31.13417346182357</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>492.1897186144911</v>
-      </c>
-      <c r="J5" t="n">
-        <v>24.42523225411054</v>
-      </c>
-      <c r="K5" t="n">
-        <v>490.4611376660615</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22.58068087670611</v>
-      </c>
-      <c r="M5" t="n">
-        <v>489.6108039166565</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20.77928266037082</v>
-      </c>
-      <c r="O5" t="n">
-        <v>488.4449750067357</v>
-      </c>
-      <c r="P5" t="n">
-        <v>22.65482830118363</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>488.8098162351443</v>
-      </c>
       <c r="R5" t="n">
-        <v>22.01259116570154</v>
+        <v>483.77</v>
       </c>
       <c r="S5" t="n">
-        <v>486.7090787757868</v>
+        <v>21.09</v>
       </c>
       <c r="T5" t="n">
-        <v>21.39588053711298</v>
+        <v>483.06</v>
       </c>
       <c r="U5" t="n">
-        <v>485.7114684791449</v>
+        <v>17.31</v>
       </c>
       <c r="V5" t="n">
-        <v>20.47038923391262</v>
+        <v>477.13</v>
       </c>
       <c r="W5" t="n">
-        <v>487.3672305608695</v>
+        <v>24.24</v>
       </c>
       <c r="X5" t="n">
-        <v>20.62089177477479</v>
+        <v>481.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>488.3061804676437</v>
+        <v>20.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.8010432539178</v>
+        <v>478.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>477.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>23.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>479.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>23.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>478.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>25.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>477.48</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>26.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>499.825</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>499.2</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>498.4625</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>498.97</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>499.0333333333334</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>499.2928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>499.39375</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>499.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>499.315</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>53.71167819943815</v>
+        <v>493.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>46.43303421774918</v>
+        <v>494.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>42.20484088051985</v>
+        <v>496.275</v>
       </c>
       <c r="AV5" t="n">
-        <v>39.25976439053093</v>
+        <v>497.07</v>
       </c>
       <c r="AW5" t="n">
-        <v>37.01169484846047</v>
+        <v>497.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>35.49114505832434</v>
+        <v>497.9357142857143</v>
       </c>
       <c r="AY5" t="n">
-        <v>34.54057340197901</v>
+        <v>498.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>33.3984821677739</v>
+        <v>498.3833333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>33.17402259298682</v>
+        <v>498.74</v>
       </c>
       <c r="BB5" t="n">
-        <v>359</v>
+        <v>47.85540721799367</v>
       </c>
       <c r="BC5" t="n">
-        <v>359</v>
+        <v>42.02511154060153</v>
       </c>
       <c r="BD5" t="n">
-        <v>359</v>
+        <v>39.42048166879751</v>
       </c>
       <c r="BE5" t="n">
-        <v>359</v>
+        <v>39.94477562835971</v>
       </c>
       <c r="BF5" t="n">
-        <v>359</v>
+        <v>39.22384478859766</v>
       </c>
       <c r="BG5" t="n">
-        <v>359</v>
+        <v>40.90532810462396</v>
       </c>
       <c r="BH5" t="n">
-        <v>359</v>
+        <v>39.88455214741667</v>
       </c>
       <c r="BI5" t="n">
-        <v>359</v>
+        <v>40.45261631423445</v>
       </c>
       <c r="BJ5" t="n">
-        <v>359</v>
+        <v>40.47162462763263</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.75</v>
+        <v>588</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.6111111111111112</v>
+        <v>588</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.4642857142857143</v>
+        <v>588</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.5526315789473685</v>
+        <v>588</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.5625</v>
+        <v>588</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.5689655172413793</v>
+        <v>588</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.5735294117647058</v>
+        <v>588</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.5897435897435898</v>
+        <v>588</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6172839506172839</v>
+        <v>588</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>477.48</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>26.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G1_478_22_REL1</t>
+          <t>S05_G1_481_21_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D6" t="n">
-        <v>32.61675315048184</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>483.7731054494039</v>
-      </c>
-      <c r="J6" t="n">
-        <v>21.09190376090798</v>
-      </c>
-      <c r="K6" t="n">
-        <v>483.0630680076054</v>
-      </c>
-      <c r="L6" t="n">
-        <v>17.30898792077956</v>
-      </c>
-      <c r="M6" t="n">
-        <v>477.127804989466</v>
-      </c>
-      <c r="N6" t="n">
-        <v>24.23930721234783</v>
-      </c>
-      <c r="O6" t="n">
-        <v>481.1519269739229</v>
-      </c>
-      <c r="P6" t="n">
-        <v>20.33293517514499</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>478.6604948525967</v>
-      </c>
       <c r="R6" t="n">
-        <v>20.10314486450589</v>
+        <v>492.19</v>
       </c>
       <c r="S6" t="n">
-        <v>477.7618207290116</v>
+        <v>24.43</v>
       </c>
       <c r="T6" t="n">
-        <v>23.78510774568929</v>
+        <v>490.46</v>
       </c>
       <c r="U6" t="n">
-        <v>479.5856113030957</v>
+        <v>22.58</v>
       </c>
       <c r="V6" t="n">
-        <v>23.43710646737965</v>
+        <v>489.61</v>
       </c>
       <c r="W6" t="n">
-        <v>478.4901488866191</v>
+        <v>20.78</v>
       </c>
       <c r="X6" t="n">
-        <v>25.24429867009603</v>
+        <v>488.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>477.4786697331532</v>
+        <v>22.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>26.32546606027358</v>
+        <v>488.81</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>22.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>486.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>485.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>20.47</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>487.37</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>20.62</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>488.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>493.4</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>494.7</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>496.275</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>497.07</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>497.8</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>497.9357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>498.4</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>498.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>498.74</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>47.85540721799367</v>
+        <v>499.825</v>
       </c>
       <c r="AT6" t="n">
-        <v>42.02511154060153</v>
+        <v>499.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>39.42048166879751</v>
+        <v>498.4625</v>
       </c>
       <c r="AV6" t="n">
-        <v>39.94477562835971</v>
+        <v>498.97</v>
       </c>
       <c r="AW6" t="n">
-        <v>39.22384478859766</v>
+        <v>499.0333333333334</v>
       </c>
       <c r="AX6" t="n">
-        <v>40.90532810462396</v>
+        <v>499.2928571428571</v>
       </c>
       <c r="AY6" t="n">
-        <v>39.88455214741667</v>
+        <v>499.39375</v>
       </c>
       <c r="AZ6" t="n">
-        <v>40.45261631423445</v>
+        <v>499.2833333333334</v>
       </c>
       <c r="BA6" t="n">
-        <v>40.47162462763263</v>
+        <v>499.315</v>
       </c>
       <c r="BB6" t="n">
-        <v>338</v>
+        <v>53.71167819943815</v>
       </c>
       <c r="BC6" t="n">
-        <v>338</v>
+        <v>46.43303421774918</v>
       </c>
       <c r="BD6" t="n">
-        <v>338</v>
+        <v>42.20484088051985</v>
       </c>
       <c r="BE6" t="n">
-        <v>338</v>
+        <v>39.25976439053093</v>
       </c>
       <c r="BF6" t="n">
-        <v>338</v>
+        <v>37.01169484846047</v>
       </c>
       <c r="BG6" t="n">
-        <v>338</v>
+        <v>35.49114505832434</v>
       </c>
       <c r="BH6" t="n">
-        <v>338</v>
+        <v>34.54057340197901</v>
       </c>
       <c r="BI6" t="n">
-        <v>338</v>
+        <v>33.3984821677739</v>
       </c>
       <c r="BJ6" t="n">
-        <v>338</v>
+        <v>33.17402259298682</v>
       </c>
       <c r="BK6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BL6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BM6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BN6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BO6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BP6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BQ6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BR6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BS6" t="n">
-        <v>588</v>
+        <v>359</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.5517241379310345</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.03448275862068965</v>
+        <v>669</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.7931034482758621</v>
+        <v>669</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.8275862068965517</v>
+        <v>669</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.8064516129032258</v>
+        <v>669</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.9375</v>
+        <v>669</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.5526315789473685</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.5689655172413793</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.5897435897435898</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.6172839506172839</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>488.31</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>21.8</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>478</v>
       </c>
       <c r="C7" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D7" t="n">
         <v>22</v>
-      </c>
-      <c r="D7" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E7" t="n">
         <v>478</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>482.1363612796375</v>
-      </c>
-      <c r="J7" t="n">
-        <v>27.24734874122436</v>
-      </c>
-      <c r="K7" t="n">
-        <v>479.644195865967</v>
-      </c>
-      <c r="L7" t="n">
-        <v>23.518875896043</v>
-      </c>
-      <c r="M7" t="n">
-        <v>477.5442572441953</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20.63738374001897</v>
-      </c>
-      <c r="O7" t="n">
-        <v>477.9311386587241</v>
-      </c>
-      <c r="P7" t="n">
-        <v>18.50619720620809</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>481.1765681923211</v>
-      </c>
       <c r="R7" t="n">
-        <v>20.31365679975748</v>
+        <v>482.14</v>
       </c>
       <c r="S7" t="n">
-        <v>480.0855741351189</v>
+        <v>27.25</v>
       </c>
       <c r="T7" t="n">
-        <v>19.76031424885554</v>
+        <v>479.64</v>
       </c>
       <c r="U7" t="n">
-        <v>478.362222688689</v>
+        <v>23.52</v>
       </c>
       <c r="V7" t="n">
-        <v>19.98410440419415</v>
+        <v>477.54</v>
       </c>
       <c r="W7" t="n">
-        <v>478.0650282746259</v>
+        <v>20.64</v>
       </c>
       <c r="X7" t="n">
-        <v>21.6515883258948</v>
+        <v>477.93</v>
       </c>
       <c r="Y7" t="n">
-        <v>477.3466720555081</v>
+        <v>18.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.1684645501572</v>
+        <v>481.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>20.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>480.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>19.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>478.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>19.98</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>478.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>21.65</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>477.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>21.17</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>495.45</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>497.0666666666667</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>498.1875</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>498.82</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>498.9166666666667</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>499.5</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>499.91875</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>500.3611111111111</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>500.47</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>60.32907673750693</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>52.19382679547032</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>47.54710657600523</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>44.4050402544576</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>41.84287739734074</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>40.30287121994448</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>39.03763758781389</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>37.70363435015087</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>37.05143856856303</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>329</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>329</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>329</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>329</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>329</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>329</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>329</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>329</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>329</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>585</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BU7" t="n">
         <v>585</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BV7" t="n">
         <v>585</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BW7" t="n">
         <v>585</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BX7" t="n">
         <v>585</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BY7" t="n">
         <v>585</v>
       </c>
-      <c r="BQ7" t="n">
+      <c r="BZ7" t="n">
         <v>585</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="CA7" t="n">
         <v>585</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="CB7" t="n">
         <v>585</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="CC7" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.95</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.78125</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.8636363636363636</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>477.35</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>21.17</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>482</v>
       </c>
       <c r="C8" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D8" t="n">
         <v>19</v>
-      </c>
-      <c r="D8" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E8" t="n">
         <v>482</v>
@@ -2328,966 +2581,1098 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>485.5198891607839</v>
-      </c>
-      <c r="J8" t="n">
-        <v>23.40323348829773</v>
-      </c>
-      <c r="K8" t="n">
-        <v>484.7047690466018</v>
-      </c>
-      <c r="L8" t="n">
-        <v>18.88826739019805</v>
-      </c>
-      <c r="M8" t="n">
-        <v>484.4626839084967</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20.60825145099125</v>
-      </c>
-      <c r="O8" t="n">
-        <v>479.0689801640401</v>
-      </c>
-      <c r="P8" t="n">
-        <v>22.21046455581102</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>478.66444186541</v>
-      </c>
       <c r="R8" t="n">
-        <v>19.94324804923765</v>
+        <v>485.52</v>
       </c>
       <c r="S8" t="n">
-        <v>482.1839608865009</v>
+        <v>23.4</v>
       </c>
       <c r="T8" t="n">
-        <v>22.06499343950198</v>
+        <v>484.7</v>
       </c>
       <c r="U8" t="n">
-        <v>483.7284998653471</v>
+        <v>18.89</v>
       </c>
       <c r="V8" t="n">
-        <v>22.0849195177669</v>
+        <v>484.46</v>
       </c>
       <c r="W8" t="n">
-        <v>484.2977524538022</v>
+        <v>20.61</v>
       </c>
       <c r="X8" t="n">
-        <v>22.77820906570064</v>
+        <v>479.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>483.922917882621</v>
+        <v>22.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.70268856611244</v>
+        <v>478.66</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>19.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>482.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>22.06</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>483.73</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>22.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>484.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>22.78</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>483.92</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>504.5</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>503.2166666666666</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>501.7</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>501.99</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>500.3583333333333</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>500.7214285714286</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>500.99375</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>501.3888888888889</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>501.165</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>52.22786612527837</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>45.56061591135727</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>43.06169991999851</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>42.68899038393857</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>40.89718731839093</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>38.97271350521007</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>37.63367788215098</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>36.51307054997778</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>38.26287724413834</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>399</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>399</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>399</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>399</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>399</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>399</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>399</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>399</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>399</v>
       </c>
-      <c r="BK8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>669</v>
-      </c>
       <c r="BT8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.05</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.8484848484848485</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.8787878787878788</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>483.92</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>24.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S09_G1_479_20_REL1</t>
+          <t>S08_G1_478_18_REL1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D9" t="n">
-        <v>29.65159377316531</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>477.005899519687</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11.50704827876147</v>
-      </c>
-      <c r="K9" t="n">
-        <v>477.7560639889214</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11.14686006763022</v>
-      </c>
-      <c r="M9" t="n">
-        <v>476.4222013687524</v>
-      </c>
-      <c r="N9" t="n">
-        <v>21.52208485790445</v>
-      </c>
-      <c r="O9" t="n">
-        <v>473.8523673352129</v>
-      </c>
-      <c r="P9" t="n">
-        <v>22.51560388347153</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>474.7443606485784</v>
-      </c>
       <c r="R9" t="n">
-        <v>20.28087332143867</v>
+        <v>462.05</v>
       </c>
       <c r="S9" t="n">
-        <v>476.1848860231511</v>
+        <v>25.1</v>
       </c>
       <c r="T9" t="n">
-        <v>25.99989259519775</v>
+        <v>462.82</v>
       </c>
       <c r="U9" t="n">
-        <v>477.6680372502497</v>
+        <v>25.61</v>
       </c>
       <c r="V9" t="n">
-        <v>26.07140759955502</v>
+        <v>466.24</v>
       </c>
       <c r="W9" t="n">
-        <v>476.8691284675377</v>
+        <v>26.43</v>
       </c>
       <c r="X9" t="n">
-        <v>25.03482682524477</v>
+        <v>470.62</v>
       </c>
       <c r="Y9" t="n">
-        <v>477.6897448655614</v>
+        <v>25.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.22682311604839</v>
+        <v>468.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>469.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>23.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>469.79</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>25.43</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>469.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>24.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>470.17</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>25.24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>498.8</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>498.9333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>499.2625</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>499.54</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>499.45</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>499.5285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>499.44375</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>499.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>499.475</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>51.4821328229513</v>
+        <v>499.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>44.34030020446662</v>
+        <v>499.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>41.18092512013298</v>
+        <v>498.225</v>
       </c>
       <c r="AV9" t="n">
-        <v>44.94828584050786</v>
+        <v>499.22</v>
       </c>
       <c r="AW9" t="n">
-        <v>43.58054803082066</v>
+        <v>498.8916666666667</v>
       </c>
       <c r="AX9" t="n">
-        <v>42.96151813910126</v>
+        <v>499.5857142857143</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.64237136859887</v>
+        <v>499.9875</v>
       </c>
       <c r="AZ9" t="n">
-        <v>41.86277516415323</v>
+        <v>500.1111111111111</v>
       </c>
       <c r="BA9" t="n">
-        <v>41.33750566979096</v>
+        <v>500.25</v>
       </c>
       <c r="BB9" t="n">
-        <v>319</v>
+        <v>62.69320138579621</v>
       </c>
       <c r="BC9" t="n">
-        <v>319</v>
+        <v>58.0173249986588</v>
       </c>
       <c r="BD9" t="n">
-        <v>319</v>
+        <v>53.976146351884</v>
       </c>
       <c r="BE9" t="n">
-        <v>319</v>
+        <v>51.07300265306515</v>
       </c>
       <c r="BF9" t="n">
-        <v>319</v>
+        <v>48.91298325143904</v>
       </c>
       <c r="BG9" t="n">
-        <v>319</v>
+        <v>47.95414263563021</v>
       </c>
       <c r="BH9" t="n">
-        <v>319</v>
+        <v>47.00239189392386</v>
       </c>
       <c r="BI9" t="n">
-        <v>319</v>
+        <v>46.3192891051868</v>
       </c>
       <c r="BJ9" t="n">
-        <v>319</v>
+        <v>45.30913263349895</v>
       </c>
       <c r="BK9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BL9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BM9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BN9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BO9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BP9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BQ9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BR9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BS9" t="n">
-        <v>640</v>
+        <v>338</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.8461538461538461</v>
+        <v>612</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.7391304347826086</v>
+        <v>612</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.7096774193548387</v>
+        <v>612</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.7419354838709677</v>
+        <v>612</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.6944444444444444</v>
+        <v>612</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.675</v>
+        <v>612</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.725</v>
+        <v>612</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.7857142857142857</v>
+        <v>612</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.8478260869565217</v>
+        <v>612</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>470.17</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>25.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S08_G1_478_18_REL1</t>
+          <t>S09_G1_479_20_REL1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D10" t="n">
-        <v>26.68643439584878</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F10" t="n">
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>462.0472304219569</v>
-      </c>
-      <c r="J10" t="n">
-        <v>25.09569891517803</v>
-      </c>
-      <c r="K10" t="n">
-        <v>462.8182632847973</v>
-      </c>
-      <c r="L10" t="n">
-        <v>25.61134641275682</v>
-      </c>
-      <c r="M10" t="n">
-        <v>466.2399280750684</v>
-      </c>
-      <c r="N10" t="n">
-        <v>26.43303078180449</v>
-      </c>
-      <c r="O10" t="n">
-        <v>470.6189566167678</v>
-      </c>
-      <c r="P10" t="n">
-        <v>25.51893506483661</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>468.4208678273292</v>
-      </c>
       <c r="R10" t="n">
-        <v>22.74487074890656</v>
+        <v>477.01</v>
       </c>
       <c r="S10" t="n">
-        <v>469.5425829666614</v>
+        <v>11.51</v>
       </c>
       <c r="T10" t="n">
-        <v>23.26097771765589</v>
+        <v>477.76</v>
       </c>
       <c r="U10" t="n">
-        <v>469.7946420122223</v>
+        <v>11.15</v>
       </c>
       <c r="V10" t="n">
-        <v>25.42626819362004</v>
+        <v>476.42</v>
       </c>
       <c r="W10" t="n">
-        <v>469.9158118057832</v>
+        <v>21.52</v>
       </c>
       <c r="X10" t="n">
-        <v>24.10503337906464</v>
+        <v>473.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>470.1662162605733</v>
+        <v>22.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>25.2439205360525</v>
+        <v>474.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>20.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>476.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>477.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>26.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>476.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>25.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>477.69</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>25.23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>499.25</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>499.3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>498.225</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>499.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>498.8916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>499.5857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>499.9875</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>500.1111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>500.25</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>62.69320138579621</v>
+        <v>498.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>58.0173249986588</v>
+        <v>498.9333333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>53.976146351884</v>
+        <v>499.2625</v>
       </c>
       <c r="AV10" t="n">
-        <v>51.07300265306515</v>
+        <v>499.54</v>
       </c>
       <c r="AW10" t="n">
-        <v>48.91298325143904</v>
+        <v>499.45</v>
       </c>
       <c r="AX10" t="n">
-        <v>47.95414263563021</v>
+        <v>499.5285714285714</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.00239189392386</v>
+        <v>499.44375</v>
       </c>
       <c r="AZ10" t="n">
-        <v>46.3192891051868</v>
+        <v>499.3833333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>45.30913263349895</v>
+        <v>499.475</v>
       </c>
       <c r="BB10" t="n">
-        <v>338</v>
+        <v>51.4821328229513</v>
       </c>
       <c r="BC10" t="n">
-        <v>338</v>
+        <v>44.34030020446662</v>
       </c>
       <c r="BD10" t="n">
-        <v>338</v>
+        <v>41.18092512013298</v>
       </c>
       <c r="BE10" t="n">
-        <v>338</v>
+        <v>44.94828584050786</v>
       </c>
       <c r="BF10" t="n">
-        <v>338</v>
+        <v>43.58054803082066</v>
       </c>
       <c r="BG10" t="n">
-        <v>338</v>
+        <v>42.96151813910126</v>
       </c>
       <c r="BH10" t="n">
-        <v>338</v>
+        <v>42.64237136859887</v>
       </c>
       <c r="BI10" t="n">
-        <v>338</v>
+        <v>41.86277516415323</v>
       </c>
       <c r="BJ10" t="n">
-        <v>338</v>
+        <v>41.33750566979096</v>
       </c>
       <c r="BK10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BL10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BM10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BN10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BO10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BP10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BQ10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BR10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BS10" t="n">
-        <v>612</v>
+        <v>319</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.75</v>
+        <v>640</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.7692307692307693</v>
+        <v>640</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.9230769230769231</v>
+        <v>640</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.9285714285714286</v>
+        <v>640</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.6666666666666666</v>
+        <v>640</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.6956521739130435</v>
+        <v>640</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.6923076923076923</v>
+        <v>640</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.7333333333333333</v>
+        <v>640</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7222222222222222</v>
+        <v>640</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.8478260869565217</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>477.69</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>25.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S12_G1_479_19_REL1</t>
+          <t>S10_G1_480_19_REL1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C11" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D11" t="n">
         <v>19</v>
       </c>
-      <c r="D11" t="n">
-        <v>28.16901408450704</v>
-      </c>
       <c r="E11" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>470.521442045393</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8.600223114826601</v>
-      </c>
-      <c r="K11" t="n">
-        <v>472.014136653606</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.89763276988777</v>
-      </c>
-      <c r="M11" t="n">
-        <v>470.4779920094438</v>
-      </c>
-      <c r="N11" t="n">
-        <v>16.03255296528514</v>
-      </c>
-      <c r="O11" t="n">
-        <v>469.4409888246754</v>
-      </c>
-      <c r="P11" t="n">
-        <v>16.57684333443302</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>471.8159122452888</v>
-      </c>
       <c r="R11" t="n">
-        <v>17.80525840299018</v>
+        <v>477.54</v>
       </c>
       <c r="S11" t="n">
-        <v>472.0503309677545</v>
+        <v>10.43</v>
       </c>
       <c r="T11" t="n">
-        <v>18.18577701545245</v>
+        <v>484.82</v>
       </c>
       <c r="U11" t="n">
-        <v>470.740844198953</v>
+        <v>20.57</v>
       </c>
       <c r="V11" t="n">
-        <v>18.36187065705889</v>
+        <v>483.68</v>
       </c>
       <c r="W11" t="n">
-        <v>472.7079901136736</v>
+        <v>23.88</v>
       </c>
       <c r="X11" t="n">
-        <v>20.20272491418754</v>
+        <v>482.16</v>
       </c>
       <c r="Y11" t="n">
-        <v>472.8258238135647</v>
+        <v>23.97</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.73470830741685</v>
+        <v>485.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>23.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>482.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>23.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>480.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>23.34</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>479.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>21.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>480.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>497.075</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>498.4166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>498.5875</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>498.27</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>498.9916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>499.0857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>499.5875</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>499.5333333333334</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>499.3</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>55.2143040796495</v>
+        <v>501.375</v>
       </c>
       <c r="AT11" t="n">
-        <v>47.95042289235369</v>
+        <v>500.4666666666666</v>
       </c>
       <c r="AU11" t="n">
-        <v>46.97092019271073</v>
+        <v>499.85</v>
       </c>
       <c r="AV11" t="n">
-        <v>48.62835695353073</v>
+        <v>500.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>46.77508165560899</v>
+        <v>499.8833333333333</v>
       </c>
       <c r="AX11" t="n">
-        <v>44.08700581387505</v>
+        <v>500.1428571428572</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.29714013361622</v>
+        <v>500.4375</v>
       </c>
       <c r="AZ11" t="n">
-        <v>42.27402669882931</v>
+        <v>500.05</v>
       </c>
       <c r="BA11" t="n">
-        <v>41.02560176280172</v>
+        <v>499.785</v>
       </c>
       <c r="BB11" t="n">
-        <v>323</v>
+        <v>53.42737477174038</v>
       </c>
       <c r="BC11" t="n">
-        <v>323</v>
+        <v>46.03204198043889</v>
       </c>
       <c r="BD11" t="n">
-        <v>323</v>
+        <v>42.65650595161306</v>
       </c>
       <c r="BE11" t="n">
-        <v>323</v>
+        <v>42.54421229732665</v>
       </c>
       <c r="BF11" t="n">
-        <v>323</v>
+        <v>40.92415410107934</v>
       </c>
       <c r="BG11" t="n">
-        <v>323</v>
+        <v>39.34001442162773</v>
       </c>
       <c r="BH11" t="n">
-        <v>323</v>
+        <v>38.55024116331829</v>
       </c>
       <c r="BI11" t="n">
-        <v>323</v>
+        <v>37.30374943919475</v>
       </c>
       <c r="BJ11" t="n">
-        <v>323</v>
+        <v>36.86894051908734</v>
       </c>
       <c r="BK11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BL11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BM11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BN11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BO11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BP11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BQ11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BR11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BS11" t="n">
-        <v>639</v>
+        <v>396</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.5333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.7727272727272727</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.8260869565217391</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.8260869565217391</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.04</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="CB11" t="n">
-        <v>0.7894736842105263</v>
+      <c r="CD11" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>23.4</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>481</v>
       </c>
       <c r="C12" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D12" t="n">
         <v>18</v>
-      </c>
-      <c r="D12" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E12" t="n">
         <v>481</v>
@@ -3312,966 +3697,1098 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>472.1359640069057</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12.36098177055418</v>
-      </c>
-      <c r="K12" t="n">
-        <v>472.9161040363436</v>
-      </c>
-      <c r="L12" t="n">
-        <v>22.99441937762892</v>
-      </c>
-      <c r="M12" t="n">
-        <v>469.7938616197945</v>
-      </c>
-      <c r="N12" t="n">
-        <v>21.11518503720542</v>
-      </c>
-      <c r="O12" t="n">
-        <v>472.5790141834128</v>
-      </c>
-      <c r="P12" t="n">
-        <v>20.04371472566419</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>475.3554637772867</v>
-      </c>
       <c r="R12" t="n">
-        <v>24.97067691804707</v>
+        <v>472.14</v>
       </c>
       <c r="S12" t="n">
-        <v>475.9682052884208</v>
+        <v>12.36</v>
       </c>
       <c r="T12" t="n">
-        <v>23.21654865533905</v>
+        <v>472.92</v>
       </c>
       <c r="U12" t="n">
-        <v>476.3176569229051</v>
+        <v>22.99</v>
       </c>
       <c r="V12" t="n">
-        <v>23.08419093543857</v>
+        <v>469.79</v>
       </c>
       <c r="W12" t="n">
-        <v>474.4810748405073</v>
+        <v>21.12</v>
       </c>
       <c r="X12" t="n">
-        <v>22.20441520134969</v>
+        <v>472.58</v>
       </c>
       <c r="Y12" t="n">
-        <v>475.6388568143034</v>
+        <v>20.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.02870403517071</v>
+        <v>475.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>24.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>475.97</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>23.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>476.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>474.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>475.64</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>22.03</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>497.55</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>498.4666666666666</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>498.7875</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>497.56</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>497.3666666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>497.0214285714285</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>496.00625</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>496.0777777777778</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>497.185</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>53.9684861748039</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>49.94445803979546</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>47.46174610936686</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>44.66795719528709</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>42.33988138334301</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>41.17861231567788</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>40.8632623628792</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>41.50869461203354</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>40.11983019654993</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>327</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>327</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>327</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>327</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>327</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>327</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>327</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>327</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>327</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>610</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>610</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>610</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>610</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>610</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>610</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>610</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>610</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>610</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.6</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.8666666666666667</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>475.64</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>22.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S10_G1_480_19_REL1</t>
+          <t>S12_G1_479_19_REL1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C13" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D13" t="n">
         <v>19</v>
       </c>
-      <c r="D13" t="n">
-        <v>28.16901408450704</v>
-      </c>
       <c r="E13" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>477.5413000997962</v>
-      </c>
-      <c r="J13" t="n">
-        <v>10.43338150519421</v>
-      </c>
-      <c r="K13" t="n">
-        <v>484.8195042868841</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20.56736856290427</v>
-      </c>
-      <c r="M13" t="n">
-        <v>483.6793700252537</v>
-      </c>
-      <c r="N13" t="n">
-        <v>23.87718061925316</v>
-      </c>
-      <c r="O13" t="n">
-        <v>482.1557951738245</v>
-      </c>
-      <c r="P13" t="n">
-        <v>23.97343227264152</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>485.1242007734772</v>
-      </c>
       <c r="R13" t="n">
-        <v>23.92885622008286</v>
+        <v>470.52</v>
       </c>
       <c r="S13" t="n">
-        <v>482.094042991812</v>
+        <v>8.6</v>
       </c>
       <c r="T13" t="n">
-        <v>23.21334505848567</v>
+        <v>472.01</v>
       </c>
       <c r="U13" t="n">
-        <v>480.4694029640264</v>
+        <v>10.9</v>
       </c>
       <c r="V13" t="n">
-        <v>23.34485416244143</v>
+        <v>470.48</v>
       </c>
       <c r="W13" t="n">
-        <v>479.9413384722836</v>
+        <v>16.03</v>
       </c>
       <c r="X13" t="n">
-        <v>21.84500576034153</v>
+        <v>469.44</v>
       </c>
       <c r="Y13" t="n">
-        <v>480.8950121587396</v>
+        <v>16.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.39619528240458</v>
+        <v>471.82</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>17.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>472.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>18.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>470.74</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>18.36</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>472.71</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>472.83</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>18.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>501.375</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>500.4666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>499.85</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>500.3</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>499.8833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>500.1428571428572</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>500.4375</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>500.05</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>499.785</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>53.42737477174038</v>
+        <v>497.075</v>
       </c>
       <c r="AT13" t="n">
-        <v>46.03204198043889</v>
+        <v>498.4166666666667</v>
       </c>
       <c r="AU13" t="n">
-        <v>42.65650595161306</v>
+        <v>498.5875</v>
       </c>
       <c r="AV13" t="n">
-        <v>42.54421229732665</v>
+        <v>498.27</v>
       </c>
       <c r="AW13" t="n">
-        <v>40.92415410107934</v>
+        <v>498.9916666666667</v>
       </c>
       <c r="AX13" t="n">
-        <v>39.34001442162773</v>
+        <v>499.0857142857143</v>
       </c>
       <c r="AY13" t="n">
-        <v>38.55024116331829</v>
+        <v>499.5875</v>
       </c>
       <c r="AZ13" t="n">
-        <v>37.30374943919475</v>
+        <v>499.5333333333334</v>
       </c>
       <c r="BA13" t="n">
-        <v>36.86894051908734</v>
+        <v>499.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>396</v>
+        <v>55.2143040796495</v>
       </c>
       <c r="BC13" t="n">
-        <v>396</v>
+        <v>47.95042289235369</v>
       </c>
       <c r="BD13" t="n">
-        <v>396</v>
+        <v>46.97092019271073</v>
       </c>
       <c r="BE13" t="n">
-        <v>396</v>
+        <v>48.62835695353073</v>
       </c>
       <c r="BF13" t="n">
-        <v>396</v>
+        <v>46.77508165560899</v>
       </c>
       <c r="BG13" t="n">
-        <v>396</v>
+        <v>44.08700581387505</v>
       </c>
       <c r="BH13" t="n">
-        <v>396</v>
+        <v>43.29714013361622</v>
       </c>
       <c r="BI13" t="n">
-        <v>396</v>
+        <v>42.27402669882931</v>
       </c>
       <c r="BJ13" t="n">
-        <v>396</v>
+        <v>41.02560176280172</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BT13" t="n">
+        <v>639</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>639</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>639</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>639</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>639</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>639</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>639</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>639</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>639</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CJ13" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BU13" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0.7666666666666667</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0.8809523809523809</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>0.8936170212765957</v>
+      <c r="CK13" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>472.83</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>18.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G1_478_20_REL1</t>
+          <t>S13_G1_480_21_REL1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D14" t="n">
-        <v>29.65159377316531</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>476.6745116259836</v>
-      </c>
-      <c r="J14" t="n">
-        <v>22.89726452902107</v>
-      </c>
-      <c r="K14" t="n">
-        <v>482.0898800585206</v>
-      </c>
-      <c r="L14" t="n">
-        <v>18.54065348705574</v>
-      </c>
-      <c r="M14" t="n">
-        <v>484.4256953647123</v>
-      </c>
-      <c r="N14" t="n">
-        <v>19.0309763976674</v>
-      </c>
-      <c r="O14" t="n">
-        <v>482.9922938665525</v>
-      </c>
-      <c r="P14" t="n">
-        <v>17.03793696118602</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>482.7743962905242</v>
-      </c>
       <c r="R14" t="n">
-        <v>16.29661377785331</v>
+        <v>466.35</v>
       </c>
       <c r="S14" t="n">
-        <v>483.7707960123702</v>
+        <v>20.48</v>
       </c>
       <c r="T14" t="n">
-        <v>18.31499380803756</v>
+        <v>464.96</v>
       </c>
       <c r="U14" t="n">
-        <v>483.9132365635136</v>
+        <v>16.9</v>
       </c>
       <c r="V14" t="n">
-        <v>18.93367023306259</v>
+        <v>465.33</v>
       </c>
       <c r="W14" t="n">
-        <v>481.7860480912504</v>
+        <v>19.28</v>
       </c>
       <c r="X14" t="n">
-        <v>21.5314416689146</v>
+        <v>468.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>481.4578986821019</v>
+        <v>17.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.43015948311356</v>
+        <v>470.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>20.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>472.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>19.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>23.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>477.24</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>24.69</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>475.46</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>23.76</v>
       </c>
       <c r="AJ14" t="n">
-        <v>496.225</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>497.15</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>497.8125</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>498.15</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>498.2583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>498.6428571428572</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>498.69375</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>498.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>497.88</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>55.37304736963643</v>
+        <v>503.175</v>
       </c>
       <c r="AT14" t="n">
-        <v>48.86164992438685</v>
+        <v>503.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>44.47642458370502</v>
+        <v>503.3625</v>
       </c>
       <c r="AV14" t="n">
-        <v>41.15880829178609</v>
+        <v>502.28</v>
       </c>
       <c r="AW14" t="n">
-        <v>38.38326367774835</v>
+        <v>502.2333333333333</v>
       </c>
       <c r="AX14" t="n">
-        <v>35.92354409587344</v>
+        <v>501.6642857142857</v>
       </c>
       <c r="AY14" t="n">
-        <v>33.93044298174576</v>
+        <v>500.69375</v>
       </c>
       <c r="AZ14" t="n">
-        <v>34.94344637331076</v>
+        <v>501.1277777777778</v>
       </c>
       <c r="BA14" t="n">
-        <v>36.82533910230834</v>
+        <v>500.805</v>
       </c>
       <c r="BB14" t="n">
-        <v>335</v>
+        <v>61.26331998022961</v>
       </c>
       <c r="BC14" t="n">
-        <v>335</v>
+        <v>54.12941283011791</v>
       </c>
       <c r="BD14" t="n">
-        <v>335</v>
+        <v>51.67742344341482</v>
       </c>
       <c r="BE14" t="n">
-        <v>335</v>
+        <v>47.94477656637895</v>
       </c>
       <c r="BF14" t="n">
-        <v>335</v>
+        <v>45.20798847794737</v>
       </c>
       <c r="BG14" t="n">
-        <v>335</v>
+        <v>43.4812949462649</v>
       </c>
       <c r="BH14" t="n">
-        <v>335</v>
+        <v>43.17507916538776</v>
       </c>
       <c r="BI14" t="n">
-        <v>335</v>
+        <v>42.21190334432477</v>
       </c>
       <c r="BJ14" t="n">
-        <v>335</v>
+        <v>41.29269880983804</v>
       </c>
       <c r="BK14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BL14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BM14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BN14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BO14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BP14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BQ14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BR14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BS14" t="n">
-        <v>610</v>
+        <v>384</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.4</v>
+        <v>669</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.44</v>
+        <v>669</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE14" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BY14" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0.9142857142857143</v>
+      <c r="CF14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>475.46</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>23.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S13_G1_480_21_REL1</t>
+          <t>S14_G1_478_20_REL1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D15" t="n">
-        <v>31.13417346182357</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>466.3455986511194</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20.47679215652614</v>
-      </c>
-      <c r="K15" t="n">
-        <v>464.9620901963985</v>
-      </c>
-      <c r="L15" t="n">
-        <v>16.90088386727006</v>
-      </c>
-      <c r="M15" t="n">
-        <v>465.3310209988546</v>
-      </c>
-      <c r="N15" t="n">
-        <v>19.28365592451929</v>
-      </c>
-      <c r="O15" t="n">
-        <v>468.1084226382767</v>
-      </c>
-      <c r="P15" t="n">
-        <v>17.78341742888311</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>470.7744491929914</v>
-      </c>
       <c r="R15" t="n">
-        <v>20.35794884687548</v>
+        <v>476.67</v>
       </c>
       <c r="S15" t="n">
-        <v>472.7308116770426</v>
+        <v>22.9</v>
       </c>
       <c r="T15" t="n">
-        <v>19.52948191538355</v>
+        <v>482.09</v>
       </c>
       <c r="U15" t="n">
-        <v>476.0026853645434</v>
+        <v>18.54</v>
       </c>
       <c r="V15" t="n">
-        <v>23.55227822111857</v>
+        <v>484.43</v>
       </c>
       <c r="W15" t="n">
-        <v>477.2382406040974</v>
+        <v>19.03</v>
       </c>
       <c r="X15" t="n">
-        <v>24.68982685122896</v>
+        <v>482.99</v>
       </c>
       <c r="Y15" t="n">
-        <v>475.4592614772044</v>
+        <v>17.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.76327167859444</v>
+        <v>482.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>483.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>18.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>483.91</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>18.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>481.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>21.53</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>481.46</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>21.43</v>
       </c>
       <c r="AJ15" t="n">
-        <v>503.175</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>503.8</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>503.3625</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>502.28</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>502.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>501.6642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>500.69375</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>501.1277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>500.805</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>61.26331998022961</v>
+        <v>496.225</v>
       </c>
       <c r="AT15" t="n">
-        <v>54.12941283011791</v>
+        <v>497.15</v>
       </c>
       <c r="AU15" t="n">
-        <v>51.67742344341482</v>
+        <v>497.8125</v>
       </c>
       <c r="AV15" t="n">
-        <v>47.94477656637895</v>
+        <v>498.15</v>
       </c>
       <c r="AW15" t="n">
-        <v>45.20798847794737</v>
+        <v>498.2583333333333</v>
       </c>
       <c r="AX15" t="n">
-        <v>43.4812949462649</v>
+        <v>498.6428571428572</v>
       </c>
       <c r="AY15" t="n">
-        <v>43.17507916538776</v>
+        <v>498.69375</v>
       </c>
       <c r="AZ15" t="n">
-        <v>42.21190334432477</v>
+        <v>498.3333333333333</v>
       </c>
       <c r="BA15" t="n">
-        <v>41.29269880983804</v>
+        <v>497.88</v>
       </c>
       <c r="BB15" t="n">
-        <v>384</v>
+        <v>55.37304736963643</v>
       </c>
       <c r="BC15" t="n">
-        <v>384</v>
+        <v>48.86164992438685</v>
       </c>
       <c r="BD15" t="n">
-        <v>384</v>
+        <v>44.47642458370502</v>
       </c>
       <c r="BE15" t="n">
-        <v>384</v>
+        <v>41.15880829178609</v>
       </c>
       <c r="BF15" t="n">
-        <v>384</v>
+        <v>38.38326367774835</v>
       </c>
       <c r="BG15" t="n">
-        <v>384</v>
+        <v>35.92354409587344</v>
       </c>
       <c r="BH15" t="n">
-        <v>384</v>
+        <v>33.93044298174576</v>
       </c>
       <c r="BI15" t="n">
-        <v>384</v>
+        <v>34.94344637331076</v>
       </c>
       <c r="BJ15" t="n">
-        <v>384</v>
+        <v>36.82533910230834</v>
       </c>
       <c r="BK15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BL15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BM15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BN15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BO15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BP15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BQ15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BR15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BS15" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.9230769230769231</v>
+        <v>610</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.8</v>
+        <v>610</v>
       </c>
       <c r="BV15" t="n">
+        <v>610</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>610</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>610</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>610</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>610</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>610</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>610</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CG15" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BW15" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.967741935483871</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.7441860465116279</v>
+      <c r="CH15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>481.46</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>21.43</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>480</v>
       </c>
       <c r="C16" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D16" t="n">
         <v>18</v>
-      </c>
-      <c r="D16" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E16" t="n">
         <v>480</v>
@@ -4296,720 +4813,819 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>458.9505029990641</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13.7183408312883</v>
-      </c>
-      <c r="K16" t="n">
-        <v>472.5298820849755</v>
-      </c>
-      <c r="L16" t="n">
-        <v>23.64297324434364</v>
-      </c>
-      <c r="M16" t="n">
-        <v>476.4973050364305</v>
-      </c>
-      <c r="N16" t="n">
-        <v>21.16333486619903</v>
-      </c>
-      <c r="O16" t="n">
-        <v>474.9113897542422</v>
-      </c>
-      <c r="P16" t="n">
-        <v>19.85966494248004</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>472.0075837460998</v>
-      </c>
       <c r="R16" t="n">
-        <v>19.8914150340186</v>
+        <v>458.95</v>
       </c>
       <c r="S16" t="n">
-        <v>475.3548834487032</v>
+        <v>13.72</v>
       </c>
       <c r="T16" t="n">
-        <v>20.47571074612351</v>
+        <v>472.53</v>
       </c>
       <c r="U16" t="n">
-        <v>478.6406744831772</v>
+        <v>23.64</v>
       </c>
       <c r="V16" t="n">
-        <v>23.13448672236008</v>
+        <v>476.5</v>
       </c>
       <c r="W16" t="n">
-        <v>477.5853350053812</v>
+        <v>21.16</v>
       </c>
       <c r="X16" t="n">
-        <v>22.23102854146062</v>
+        <v>474.91</v>
       </c>
       <c r="Y16" t="n">
-        <v>477.6548218164711</v>
+        <v>19.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.1921170097521</v>
+        <v>472.01</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>19.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>475.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>20.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>478.64</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>23.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>477.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>22.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>477.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>21.19</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>503.4</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>500.8</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>500.1875</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>501</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>500.85</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>500.9571428571429</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>500.8625</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>500.2888888888889</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>500.26</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>59.18944162601975</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>54.30125842617893</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>49.21358901512873</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>44.91948352329977</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>43.46620334620144</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>41.7504271027891</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>40.07921648123875</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>39.011463968783</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>37.77886181451209</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>355</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>355</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>355</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>355</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>355</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>355</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>355</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>355</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>355</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.625</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.625</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.7407407407407407</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.84375</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.875</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>477.65</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>21.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G1_478_22_REL1</t>
+          <t>S16_G1_481_18_REL1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D17" t="n">
-        <v>32.61675315048184</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>469.6053730391642</v>
-      </c>
-      <c r="J17" t="n">
-        <v>24.29375328763858</v>
-      </c>
-      <c r="K17" t="n">
-        <v>476.6532240784994</v>
-      </c>
-      <c r="L17" t="n">
-        <v>20.32918811375724</v>
-      </c>
-      <c r="M17" t="n">
-        <v>482.0219952800343</v>
-      </c>
-      <c r="N17" t="n">
-        <v>24.74284455251832</v>
-      </c>
-      <c r="O17" t="n">
-        <v>482.8493855152603</v>
-      </c>
-      <c r="P17" t="n">
-        <v>24.71639481637034</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>482.1234782354454</v>
-      </c>
       <c r="R17" t="n">
-        <v>25.79298135072496</v>
+        <v>483.5</v>
       </c>
       <c r="S17" t="n">
-        <v>483.2759297363214</v>
+        <v>15.08</v>
       </c>
       <c r="T17" t="n">
-        <v>25.42533760971919</v>
+        <v>483.58</v>
       </c>
       <c r="U17" t="n">
-        <v>478.6901130746404</v>
+        <v>17.66</v>
       </c>
       <c r="V17" t="n">
-        <v>25.38985596215311</v>
+        <v>482.82</v>
       </c>
       <c r="W17" t="n">
-        <v>479.1607331140012</v>
+        <v>19.78</v>
       </c>
       <c r="X17" t="n">
-        <v>26.19973106535928</v>
+        <v>484.37</v>
       </c>
       <c r="Y17" t="n">
-        <v>478.1806854463907</v>
+        <v>17.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>27.24455659083762</v>
+        <v>482.42</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>484.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>18.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>484.86</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>19.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>482.39</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>19.89</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>481.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>502.675</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>500.95</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>500.9125</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>500.48</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>500.3416666666666</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>500.1</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>500.2</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>499.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>499.76</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>52.90906703959161</v>
+        <v>500.725</v>
       </c>
       <c r="AT17" t="n">
-        <v>47.62857160710715</v>
+        <v>500.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>43.73276624854641</v>
+        <v>500.2875</v>
       </c>
       <c r="AV17" t="n">
-        <v>41.49927228277623</v>
+        <v>500.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>40.0879233338698</v>
+        <v>500.2583333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>39.62634405111255</v>
+        <v>500.3214285714286</v>
       </c>
       <c r="AY17" t="n">
-        <v>38.48600394948792</v>
+        <v>500.56875</v>
       </c>
       <c r="AZ17" t="n">
-        <v>37.87969259525625</v>
+        <v>500.6166666666667</v>
       </c>
       <c r="BA17" t="n">
-        <v>37.46508241015893</v>
+        <v>500.645</v>
       </c>
       <c r="BB17" t="n">
-        <v>373</v>
+        <v>55.04361338974758</v>
       </c>
       <c r="BC17" t="n">
-        <v>373</v>
+        <v>46.58261478277062</v>
       </c>
       <c r="BD17" t="n">
-        <v>373</v>
+        <v>41.72594928518703</v>
       </c>
       <c r="BE17" t="n">
-        <v>373</v>
+        <v>38.40790934169679</v>
       </c>
       <c r="BF17" t="n">
-        <v>373</v>
+        <v>35.94590747065497</v>
       </c>
       <c r="BG17" t="n">
-        <v>373</v>
+        <v>33.97820054453882</v>
       </c>
       <c r="BH17" t="n">
-        <v>373</v>
+        <v>32.35537472256348</v>
       </c>
       <c r="BI17" t="n">
-        <v>373</v>
+        <v>31.11006893095688</v>
       </c>
       <c r="BJ17" t="n">
-        <v>373</v>
+        <v>30.14181439462462</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.4583333333333333</v>
+        <v>669</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.4705882352941176</v>
+        <v>669</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.5660377358490566</v>
+        <v>669</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.5737704918032787</v>
+        <v>669</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.5633802816901409</v>
+        <v>669</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.5432098765432098</v>
+        <v>669</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.5494505494505495</v>
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.5287356321839081</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>481.6</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>19.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S16_G1_481_18_REL1</t>
+          <t>S17_G1_478_22_REL1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D18" t="n">
-        <v>26.68643439584878</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>483.5001980443575</v>
-      </c>
-      <c r="J18" t="n">
-        <v>15.08286361576831</v>
-      </c>
-      <c r="K18" t="n">
-        <v>483.579437172752</v>
-      </c>
-      <c r="L18" t="n">
-        <v>17.6612964531498</v>
-      </c>
-      <c r="M18" t="n">
-        <v>482.8238973689179</v>
-      </c>
-      <c r="N18" t="n">
-        <v>19.78025081650843</v>
-      </c>
-      <c r="O18" t="n">
-        <v>484.3728206516905</v>
-      </c>
-      <c r="P18" t="n">
-        <v>17.41498978840576</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>482.4229279851246</v>
-      </c>
       <c r="R18" t="n">
-        <v>17.69557035878163</v>
+        <v>469.61</v>
       </c>
       <c r="S18" t="n">
-        <v>484.1379430036966</v>
+        <v>24.29</v>
       </c>
       <c r="T18" t="n">
-        <v>18.55959644244792</v>
+        <v>476.65</v>
       </c>
       <c r="U18" t="n">
-        <v>484.863025982983</v>
+        <v>20.33</v>
       </c>
       <c r="V18" t="n">
-        <v>19.73477221916049</v>
+        <v>482.02</v>
       </c>
       <c r="W18" t="n">
-        <v>482.3931268184434</v>
+        <v>24.74</v>
       </c>
       <c r="X18" t="n">
-        <v>19.89299727099431</v>
+        <v>482.85</v>
       </c>
       <c r="Y18" t="n">
-        <v>481.5963961127233</v>
+        <v>24.72</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.50383100179878</v>
+        <v>482.12</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>25.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>483.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>25.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>478.69</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>25.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>479.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>478.18</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>27.24</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500.725</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>500.6</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>500.2875</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>500.25</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>500.2583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>500.3214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>500.56875</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>500.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>500.645</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>55.04361338974758</v>
+        <v>502.675</v>
       </c>
       <c r="AT18" t="n">
-        <v>46.58261478277062</v>
+        <v>500.95</v>
       </c>
       <c r="AU18" t="n">
-        <v>41.72594928518703</v>
+        <v>500.9125</v>
       </c>
       <c r="AV18" t="n">
-        <v>38.40790934169679</v>
+        <v>500.48</v>
       </c>
       <c r="AW18" t="n">
-        <v>35.94590747065497</v>
+        <v>500.3416666666666</v>
       </c>
       <c r="AX18" t="n">
-        <v>33.97820054453882</v>
+        <v>500.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>32.35537472256348</v>
+        <v>500.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>31.11006893095688</v>
+        <v>499.8666666666667</v>
       </c>
       <c r="BA18" t="n">
-        <v>30.14181439462462</v>
+        <v>499.76</v>
       </c>
       <c r="BB18" t="n">
-        <v>357</v>
+        <v>52.90906703959161</v>
       </c>
       <c r="BC18" t="n">
-        <v>357</v>
+        <v>47.62857160710715</v>
       </c>
       <c r="BD18" t="n">
-        <v>357</v>
+        <v>43.73276624854641</v>
       </c>
       <c r="BE18" t="n">
-        <v>357</v>
+        <v>41.49927228277623</v>
       </c>
       <c r="BF18" t="n">
-        <v>357</v>
+        <v>40.0879233338698</v>
       </c>
       <c r="BG18" t="n">
-        <v>357</v>
+        <v>39.62634405111255</v>
       </c>
       <c r="BH18" t="n">
-        <v>357</v>
+        <v>38.48600394948792</v>
       </c>
       <c r="BI18" t="n">
-        <v>357</v>
+        <v>37.87969259525625</v>
       </c>
       <c r="BJ18" t="n">
-        <v>357</v>
+        <v>37.46508241015893</v>
       </c>
       <c r="BK18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BL18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BM18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BN18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BO18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BP18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BQ18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BR18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BS18" t="n">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.1111111111111111</v>
+        <v>669</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.8235294117647058</v>
+        <v>669</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.7037037037037037</v>
+        <v>669</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.5945945945945946</v>
+        <v>669</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.5531914893617021</v>
+        <v>669</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.01754385964912281</v>
+        <v>669</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.5373134328358209</v>
+        <v>669</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.5324675324675324</v>
+        <v>669</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.5287356321839081</v>
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.5660377358490566</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.5633802816901409</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.5432098765432098</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.5494505494505495</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>478.18</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>27.24</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>482</v>
       </c>
       <c r="C19" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D19" t="n">
         <v>22</v>
-      </c>
-      <c r="D19" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E19" t="n">
         <v>482</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>481.1955165874411</v>
-      </c>
-      <c r="J19" t="n">
-        <v>25.63071039805131</v>
-      </c>
-      <c r="K19" t="n">
-        <v>479.3785332783445</v>
-      </c>
-      <c r="L19" t="n">
-        <v>20.53856691098629</v>
-      </c>
-      <c r="M19" t="n">
-        <v>483.5564725843977</v>
-      </c>
-      <c r="N19" t="n">
-        <v>22.0766209594706</v>
-      </c>
-      <c r="O19" t="n">
-        <v>480.5910734569295</v>
-      </c>
-      <c r="P19" t="n">
-        <v>23.3203006061428</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>478.4133297543536</v>
-      </c>
       <c r="R19" t="n">
-        <v>22.11721810192367</v>
+        <v>481.2</v>
       </c>
       <c r="S19" t="n">
-        <v>483.0506418319919</v>
+        <v>25.63</v>
       </c>
       <c r="T19" t="n">
-        <v>22.88750401624729</v>
+        <v>479.38</v>
       </c>
       <c r="U19" t="n">
-        <v>480.5750223834752</v>
+        <v>20.54</v>
       </c>
       <c r="V19" t="n">
-        <v>20.83366620349993</v>
+        <v>483.56</v>
       </c>
       <c r="W19" t="n">
-        <v>482.2946416279033</v>
+        <v>22.08</v>
       </c>
       <c r="X19" t="n">
-        <v>21.82532338301203</v>
+        <v>480.59</v>
       </c>
       <c r="Y19" t="n">
-        <v>481.125753230176</v>
+        <v>23.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.58311867480892</v>
+        <v>478.41</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>22.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>483.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>22.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>480.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>20.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>482.29</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>21.83</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>481.13</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>22.58</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>505.2</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>503.35</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>502.575</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>502.18</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>501.6416666666667</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>501.6357142857143</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>501.575</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>501.2666666666667</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>501.39</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>53.37330793570884</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>48.12269907919408</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>44.37729571526413</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>41.87872490895586</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>39.96765271927898</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>37.59601246224425</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>35.50379381136613</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>34.38856399056718</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>36.32764649684865</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>369</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>369</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>369</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>369</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>369</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>369</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>369</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>369</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>369</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>1</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.7407407407407407</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.8387096774193549</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.926829268292683</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.9512195121951219</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.9761904761904762</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.9534883720930233</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>481.13</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>22.58</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>479</v>
       </c>
       <c r="C20" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D20" t="n">
         <v>18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E20" t="n">
         <v>479</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
+        <v>78</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>REL1</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>480.58</v>
+      </c>
+      <c r="S20" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>479.28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="V20" t="n">
+        <v>480.38</v>
+      </c>
+      <c r="W20" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>478.32</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>477.96</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>477.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>476.95</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>477.28</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>476.88</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>499.875</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>499.8833333333333</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>499.7375</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>499.85</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>500.0833333333333</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>500.9571428571429</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>500.575</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>500.2833333333334</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>500.46</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>50.69624616280775</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>46.33216725151352</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>44.31894170385841</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>43.37519452405949</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>44.21963804565669</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>42.13242243698033</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>41.44507660748138</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>39.55562539007568</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>38.79495328003373</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>325</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>639</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>639</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>639</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>639</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>639</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>639</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>639</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>639</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>639</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.7</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>REL1</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>480.579362886321</v>
-      </c>
-      <c r="J20" t="n">
-        <v>16.40133195412044</v>
-      </c>
-      <c r="K20" t="n">
-        <v>479.2808598413001</v>
-      </c>
-      <c r="L20" t="n">
-        <v>16.3420683665587</v>
-      </c>
-      <c r="M20" t="n">
-        <v>480.3818357017166</v>
-      </c>
-      <c r="N20" t="n">
-        <v>15.02734249379201</v>
-      </c>
-      <c r="O20" t="n">
-        <v>478.3194766723334</v>
-      </c>
-      <c r="P20" t="n">
-        <v>16.84856092194789</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>477.9647319768264</v>
-      </c>
-      <c r="R20" t="n">
-        <v>18.50987833259893</v>
-      </c>
-      <c r="S20" t="n">
-        <v>477.1486604140424</v>
-      </c>
-      <c r="T20" t="n">
-        <v>17.565849677014</v>
-      </c>
-      <c r="U20" t="n">
-        <v>476.950602429792</v>
-      </c>
-      <c r="V20" t="n">
-        <v>18.28943662339969</v>
-      </c>
-      <c r="W20" t="n">
-        <v>477.2811160114005</v>
-      </c>
-      <c r="X20" t="n">
-        <v>18.51963556655212</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>476.8788698201976</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>18.07249672279795</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>499.875</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>499.8833333333333</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>499.7375</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>499.85</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>500.0833333333333</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>500.9571428571429</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>500.575</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>500.2833333333334</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>500.46</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>50.69624616280775</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>46.33216725151352</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>44.31894170385841</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>43.37519452405949</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>44.21963804565669</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>42.13242243698033</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>41.44507660748138</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>39.55562539007568</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>38.79495328003373</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>325</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>639</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9655172413793104</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.7631578947368421</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.7380952380952381</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>476.88</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>18.07</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>481</v>
       </c>
       <c r="C21" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D21" t="n">
         <v>20</v>
-      </c>
-      <c r="D21" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E21" t="n">
         <v>481</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>479.9473060971784</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20.91661106055653</v>
-      </c>
-      <c r="K21" t="n">
-        <v>480.5983346272472</v>
-      </c>
-      <c r="L21" t="n">
-        <v>28.97111595038043</v>
-      </c>
-      <c r="M21" t="n">
-        <v>478.1477509829188</v>
-      </c>
-      <c r="N21" t="n">
-        <v>25.81135259971711</v>
-      </c>
-      <c r="O21" t="n">
-        <v>476.6643941522053</v>
-      </c>
-      <c r="P21" t="n">
-        <v>23.05599901959109</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>477.2061770625701</v>
-      </c>
       <c r="R21" t="n">
-        <v>24.51655713254487</v>
+        <v>479.95</v>
       </c>
       <c r="S21" t="n">
-        <v>478.9215565028694</v>
+        <v>20.92</v>
       </c>
       <c r="T21" t="n">
-        <v>23.181038055063</v>
+        <v>480.6</v>
       </c>
       <c r="U21" t="n">
-        <v>480.3980228024046</v>
+        <v>28.97</v>
       </c>
       <c r="V21" t="n">
-        <v>22.65711648295748</v>
+        <v>478.15</v>
       </c>
       <c r="W21" t="n">
-        <v>481.1095815359148</v>
+        <v>25.81</v>
       </c>
       <c r="X21" t="n">
-        <v>21.8229749118456</v>
+        <v>476.66</v>
       </c>
       <c r="Y21" t="n">
-        <v>481.6581501594585</v>
+        <v>23.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.86361743923686</v>
+        <v>477.21</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>24.52</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>478.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>23.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>480.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>22.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>481.11</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>21.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>481.66</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>21.86</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>504.55</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>505.15</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>503.4125</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>502.99</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>502.8166666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>502.7</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>502.46875</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>502.3</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>502.395</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>53.72287687754631</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>53.57294870859111</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>51.776127160594</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>48.50164842559477</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>45.60153201617487</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>43.37571736747252</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>41.48959536362701</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>40.28466760995359</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>38.79960019123908</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>398</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>398</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>398</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>398</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>398</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>398</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>398</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>398</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>398</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>1</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.8125</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.6923076923076923</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>481.66</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>21.86</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>479.65</v>
       </c>
       <c r="C22" t="n">
+        <v>29.42920681986657</v>
+      </c>
+      <c r="D22" t="n">
         <v>19.85</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29.42920681986657</v>
       </c>
       <c r="E22" t="n">
         <v>479.65</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>77.84999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.282</v>
+      </c>
       <c r="I22" t="n">
-        <v>477.1435095407368</v>
+        <v>2.266</v>
       </c>
       <c r="J22" t="n">
-        <v>19.02728114462595</v>
+        <v>2.273</v>
       </c>
       <c r="K22" t="n">
-        <v>478.2211310694432</v>
+        <v>2.270499999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>20.30793441382937</v>
+        <v>2.262</v>
       </c>
       <c r="M22" t="n">
-        <v>478.1443888618682</v>
+        <v>2.2645</v>
       </c>
       <c r="N22" t="n">
-        <v>21.61819318419944</v>
+        <v>2.3565</v>
       </c>
       <c r="O22" t="n">
-        <v>478.0825444796133</v>
+        <v>2.2675</v>
       </c>
       <c r="P22" t="n">
-        <v>21.48779701961763</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>478.1135863111134</v>
-      </c>
+        <v>2.2325</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>21.67546243122408</v>
+        <v>477.1445</v>
       </c>
       <c r="S22" t="n">
-        <v>478.7569032348776</v>
+        <v>19.0275</v>
       </c>
       <c r="T22" t="n">
-        <v>22.18895221892767</v>
+        <v>478.2205</v>
       </c>
       <c r="U22" t="n">
-        <v>478.8984672436849</v>
+        <v>20.308</v>
       </c>
       <c r="V22" t="n">
-        <v>22.3809888209659</v>
+        <v>478.1439999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>478.7521477165181</v>
+        <v>21.618</v>
       </c>
       <c r="X22" t="n">
-        <v>22.69586491795817</v>
+        <v>478.082</v>
       </c>
       <c r="Y22" t="n">
-        <v>478.6749325955275</v>
+        <v>21.488</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.80728186635786</v>
+        <v>478.1129999999999</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>21.676</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>478.756</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>22.1895</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>478.898</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>22.3795</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>478.753</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>22.6955</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>478.6764999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>22.806</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500.5912500000001</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>500.3516666666666</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>500.1925</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>500.5925</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>500.352</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>500.1924999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>500.083</v>
       </c>
-      <c r="AN22" t="n">
-        <v>499.9950000000001</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>500.1271428571429</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>500.1225000000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>500.0477777777777</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AW22" t="n">
+        <v>499.9945</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>500.1274999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>500.1214999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>500.047</v>
+      </c>
+      <c r="BA22" t="n">
         <v>500.0314999999999</v>
       </c>
-      <c r="AS22" t="n">
-        <v>54.73855700793805</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>49.15586175096202</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>45.94137881098382</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>44.31406704884454</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>42.68165560931723</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>41.11676213705158</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>39.97835475204147</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>39.17982659575303</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>38.7862996123315</v>
-      </c>
       <c r="BB22" t="n">
+        <v>54.738</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>49.15500000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>45.9415</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>44.314</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>42.682</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>41.1165</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>39.9785</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>39.17899999999999</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>38.786</v>
+      </c>
+      <c r="BK22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>357.35</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>647.55</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6903923853923852</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7345437368116398</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6944623149253287</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6939146800402762</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7960723054392134</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.722900929676374</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7848833365067414</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.7677222372559611</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8053343525462873</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>478.6764999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>22.806</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.424411235711461</v>
       </c>
       <c r="C23" t="n">
+        <v>2.369931877634437</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.598519051464429</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.369931877634437</v>
       </c>
       <c r="E23" t="n">
         <v>1.424411235711461</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02769191407727457</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.670959384053932</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2625301987641762</v>
+      </c>
       <c r="I23" t="n">
-        <v>8.402085596647558</v>
+        <v>0.2784430396253235</v>
       </c>
       <c r="J23" t="n">
-        <v>5.693584488001615</v>
+        <v>0.2579698064747725</v>
       </c>
       <c r="K23" t="n">
-        <v>6.637648459325153</v>
+        <v>0.2534078260744713</v>
       </c>
       <c r="L23" t="n">
-        <v>4.712608286264449</v>
+        <v>0.255087188396851</v>
       </c>
       <c r="M23" t="n">
-        <v>6.311138104015247</v>
+        <v>0.2475240551840101</v>
       </c>
       <c r="N23" t="n">
-        <v>3.013062864246195</v>
+        <v>0.2391492597125331</v>
       </c>
       <c r="O23" t="n">
-        <v>5.240338587954841</v>
+        <v>0.2452683814668504</v>
       </c>
       <c r="P23" t="n">
-        <v>3.330552859382865</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.046609109924156</v>
-      </c>
+        <v>0.2596531086702127</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>2.9921144014923</v>
+        <v>8.40143250629883</v>
       </c>
       <c r="S23" t="n">
-        <v>4.609803528933207</v>
+        <v>5.694420976987731</v>
       </c>
       <c r="T23" t="n">
-        <v>2.824643769798718</v>
+        <v>6.637365104189748</v>
       </c>
       <c r="U23" t="n">
-        <v>4.085975220024822</v>
+        <v>4.711824543243921</v>
       </c>
       <c r="V23" t="n">
-        <v>2.431562064434699</v>
+        <v>6.311348508837075</v>
       </c>
       <c r="W23" t="n">
-        <v>3.985043412900909</v>
+        <v>3.012585181149938</v>
       </c>
       <c r="X23" t="n">
-        <v>2.184471037801671</v>
+        <v>5.239738442648489</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.953218625707804</v>
+        <v>3.331065263466581</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.490260022578424</v>
+        <v>5.045959404889172</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.992100828585336</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>4.610558134953876</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.824049863507892</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.086350321175169</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.432532739001839</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>3.984447528235649</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.18467985128979</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.952988576281311</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.491151498699684</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.412479757024983</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.616467754200674</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.032464313145633</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.413385223529648</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.616165534759445</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.032257948298168</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.698123112516628</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.439111161680188</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.359306940991689</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.358579281629773</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.368654238641478</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.205208106074365</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>3.694488489445896</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.171412030172858</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.236065835019313</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.747157742597219</v>
-      </c>
       <c r="AW23" t="n">
-        <v>3.953736038019475</v>
+        <v>1.438601202923394</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.800922627807212</v>
+        <v>1.359035551992278</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.036780802971008</v>
+        <v>1.357630579161246</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.976232951785967</v>
+        <v>1.369076138746205</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.460463899910232</v>
+        <v>1.204265554732752</v>
       </c>
       <c r="BB23" t="n">
-        <v>26.93515605261917</v>
+        <v>3.69317093822468</v>
       </c>
       <c r="BC23" t="n">
-        <v>26.93515605261917</v>
+        <v>4.171521872990971</v>
       </c>
       <c r="BD23" t="n">
-        <v>26.93515605261917</v>
+        <v>4.236403980289241</v>
       </c>
       <c r="BE23" t="n">
-        <v>26.93515605261917</v>
+        <v>3.74653299380697</v>
       </c>
       <c r="BF23" t="n">
-        <v>26.93515605261917</v>
+        <v>3.954290940498089</v>
       </c>
       <c r="BG23" t="n">
-        <v>26.93515605261917</v>
+        <v>3.800212286314099</v>
       </c>
       <c r="BH23" t="n">
-        <v>26.93515605261917</v>
+        <v>4.036920758514628</v>
       </c>
       <c r="BI23" t="n">
-        <v>26.93515605261917</v>
+        <v>3.976280859507313</v>
       </c>
       <c r="BJ23" t="n">
-        <v>26.93515605261917</v>
+        <v>3.46062726288625</v>
       </c>
       <c r="BK23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>26.93515605261918</v>
+      </c>
+      <c r="BT23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>30.14609165555733</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.1954339123455305</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.1536049563400427</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2061827818314617</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2634153453681317</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1361028610286621</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2565436365935443</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2278389083937423</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2172025008988688</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.129720036094527</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.952988576281311</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>2.491151498699684</v>
       </c>
     </row>
   </sheetData>
